--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_p_monto_aps_a_2020_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_p_monto_aps_a_2020_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:45</t>
+    <t xml:space="preserve">2026-09-18 09:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_p_monto_aps_a_2020_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_p_monto_aps_a_2020_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:05</t>
+    <t xml:space="preserve">2026-10-05 04:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -658,7 +658,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>84757.12</v>
+        <v>84757.13</v>
       </c>
     </row>
     <row r="3">
